--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/ALABAMA_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/ALABAMA_2020.xlsx
@@ -2328,7 +2328,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C110">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C170">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C177">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C186">
@@ -4891,7 +4891,7 @@
         <v>33</v>
       </c>
       <c r="D252">
-        <v>0.009254066180594503</v>
+        <v>0.009254066180594505</v>
       </c>
     </row>
     <row r="253">
@@ -6871,7 +6871,7 @@
         <v>35</v>
       </c>
       <c r="D362">
-        <v>0.009814918676388109</v>
+        <v>0.009814918676388108</v>
       </c>
     </row>
     <row r="363">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C465">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C562">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Amaxac De Guerero</t>
+          <t>Amaxac De Guerrero</t>
         </is>
       </c>
       <c r="C660">
@@ -14197,7 +14197,7 @@
         <v>33</v>
       </c>
       <c r="D769">
-        <v>0.009254066180594503</v>
+        <v>0.009254066180594505</v>
       </c>
     </row>
     <row r="770">
